--- a/data/module_owner_mapping.xlsx
+++ b/data/module_owner_mapping.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17985" windowHeight="8895"/>
+    <workbookView windowWidth="29400" windowHeight="12260"/>
   </bookViews>
   <sheets>
     <sheet name="模块负责人映射" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>模块ID</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>134xxxx</t>
+  </si>
+  <si>
+    <t>emqx_client</t>
+  </si>
+  <si>
+    <t>命令下发</t>
+  </si>
+  <si>
+    <t>龙九</t>
   </si>
 </sst>
 </file>
@@ -180,8 +189,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
+      <color rgb="FFBBBEBF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -634,19 +643,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -655,7 +664,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -779,8 +788,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1127,8 +1139,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="6"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1360,6 +1372,35 @@
         <v>18</v>
       </c>
     </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
